--- a/scenario_data/lithium_projects_list.xlsx
+++ b/scenario_data/lithium_projects_list.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/scenario_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1441" documentId="11_AD4DB114E441178AC67DF4902691E15C683EDF20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EC37A3A-F152-4A44-B165-FCB398C56078}"/>
+  <xr:revisionPtr revIDLastSave="1615" documentId="11_AD4DB114E441178AC67DF4902691E15C683EDF20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{765C1F83-4940-4420-AE39-D3FDA1FB502F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">map!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">map!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="126">
   <si>
     <t>df_rotary_dryer_Chaerhan</t>
   </si>
@@ -245,9 +245,6 @@
     <t>Prefeas/Scoping</t>
   </si>
   <si>
-    <t>Feasibility Started</t>
-  </si>
-  <si>
     <t>Construction Planned</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>Feasibility Complete</t>
   </si>
   <si>
-    <t>Reserves Development</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -308,12 +302,6 @@
     <t>Salar del Hombre Muerto North</t>
   </si>
   <si>
-    <t>Chemical-based</t>
-  </si>
-  <si>
-    <t>Ion-exchanger</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -336,13 +324,106 @@
   </si>
   <si>
     <t>https://www.zijinmining.com/global/program-detail-71747.htm</t>
+  </si>
+  <si>
+    <t>Evaporitic</t>
+  </si>
+  <si>
+    <t>Electricity supply</t>
+  </si>
+  <si>
+    <t>Heat supply</t>
+  </si>
+  <si>
+    <t>natural_gas</t>
+  </si>
+  <si>
+    <t>electricity_grid</t>
+  </si>
+  <si>
+    <t>diesel</t>
+  </si>
+  <si>
+    <t>propane</t>
+  </si>
+  <si>
+    <t>natural_gas_CHP</t>
+  </si>
+  <si>
+    <t>Same energy source as Cauchari-Olaroz</t>
+  </si>
+  <si>
+    <t>electric_boiler</t>
+  </si>
+  <si>
+    <t>diesel_CHP</t>
+  </si>
+  <si>
+    <t>US-WECC</t>
+  </si>
+  <si>
+    <t>Centenario</t>
+  </si>
+  <si>
+    <t>Atacama</t>
+  </si>
+  <si>
+    <t>Olaroz</t>
+  </si>
+  <si>
+    <t>Arizaro</t>
+  </si>
+  <si>
+    <t>Tolillar</t>
+  </si>
+  <si>
+    <t>Rincon</t>
+  </si>
+  <si>
+    <t>Uyuni</t>
+  </si>
+  <si>
+    <t>name_figure</t>
+  </si>
+  <si>
+    <t>Cauchari-\nOlaroz</t>
+  </si>
+  <si>
+    <t>Tres\nQuebradas</t>
+  </si>
+  <si>
+    <t>Pastos\nGrandes</t>
+  </si>
+  <si>
+    <t>Qinghai\nYiliping</t>
+  </si>
+  <si>
+    <t>East\nTaijinar</t>
+  </si>
+  <si>
+    <t>Lakkor\nTso</t>
+  </si>
+  <si>
+    <t>Silver\nPeak</t>
+  </si>
+  <si>
+    <t>Hombre\nMuerto\nNorth</t>
+  </si>
+  <si>
+    <t>Upper\nRhine\nGraben</t>
+  </si>
+  <si>
+    <t>Sal\nde los\nAngeles</t>
+  </si>
+  <si>
+    <t>Sal de\nVida</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,6 +477,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -435,7 +524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -445,9 +534,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -459,9 +545,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -479,7 +562,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -487,7 +571,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -771,40 +883,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60DA4C04-C08C-42E7-81A2-6ED32579CCCF}">
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" style="9" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="39.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="99.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="2" customWidth="1"/>
+    <col min="12" max="12" width="23" style="2" customWidth="1"/>
+    <col min="13" max="13" width="99.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="13"/>
+    <col min="15" max="15" width="29.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.7109375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>54</v>
@@ -816,12 +932,21 @@
         <v>60</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>44</v>
@@ -832,25 +957,34 @@
       <c r="D2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>65</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="8">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J2" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>37</v>
@@ -859,12 +993,12 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -873,13 +1007,22 @@
       <c r="H3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="8">
         <v>6.6169154228855711E-4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -890,10 +1033,10 @@
       <c r="D4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -902,16 +1045,25 @@
       <c r="H4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="8">
         <v>3.0901639344262203E-4</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>32</v>
@@ -920,12 +1072,12 @@
         <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -934,16 +1086,25 @@
       <c r="H5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>33</v>
@@ -952,12 +1113,12 @@
         <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -966,14 +1127,23 @@
       <c r="H6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <v>2.0000000000000001E-4</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -984,13 +1154,13 @@
         <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>65</v>
+        <v>88</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>55</v>
@@ -998,14 +1168,23 @@
       <c r="H7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="8">
         <v>2.1999999999999998E-4</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1018,23 +1197,32 @@
       <c r="D8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="14" t="s">
-        <v>65</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="8">
         <v>1.5E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -1047,25 +1235,37 @@
       <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="8">
         <v>6.39141205615194E-4</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>34</v>
@@ -1076,10 +1276,10 @@
       <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" s="14" t="s">
+      <c r="E10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1088,14 +1288,23 @@
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="8">
         <v>2.1999999999999998E-4</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -1106,25 +1315,34 @@
         <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="8">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -1137,26 +1355,35 @@
       <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="8">
         <v>9.4987873888439695E-4</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
@@ -1167,25 +1394,34 @@
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>8.0000000000000004E-4</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1199,10 +1435,10 @@
         <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>55</v>
@@ -1210,13 +1446,22 @@
       <c r="H14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="4">
+      <c r="I14" s="8">
         <v>1.9262295081967198E-4</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>88</v>
+      <c r="J14" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
@@ -1231,19 +1476,28 @@
         <v>67</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="8">
         <v>6.6169154228855711E-4</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -1257,10 +1511,10 @@
         <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>55</v>
@@ -1268,11 +1522,20 @@
       <c r="H16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="8">
         <v>2.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1286,24 +1549,33 @@
         <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="8">
         <v>9.1967213114754103E-4</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>40</v>
@@ -1315,24 +1587,33 @@
         <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="8">
         <v>3.55737704918032E-4</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>57</v>
@@ -1347,7 +1628,7 @@
         <v>67</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>55</v>
@@ -1355,14 +1636,23 @@
       <c r="H19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="8">
         <v>1.6967213114754001E-4</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
@@ -1379,21 +1669,30 @@
         <v>66</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="8">
         <v>7.8200000000000003E-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>45</v>
@@ -1408,7 +1707,7 @@
         <v>67</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>55</v>
@@ -1416,11 +1715,20 @@
       <c r="H21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="8">
         <v>2.6065573770491803E-4</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
@@ -1437,7 +1745,7 @@
         <v>67</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>55</v>
@@ -1445,11 +1753,20 @@
       <c r="H22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="8">
         <v>2.6166666666666596E-4</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>24</v>
       </c>
@@ -1462,11 +1779,11 @@
       <c r="D23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>94</v>
+      <c r="E23" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>55</v>
@@ -1474,13 +1791,22 @@
       <c r="H23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="8">
         <v>2.8688524590163902E-4</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>35</v>
@@ -1492,10 +1818,10 @@
         <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>55</v>
@@ -1503,13 +1829,22 @@
       <c r="H24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="8">
         <v>6.9999999999999891E-4</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>41</v>
@@ -1521,10 +1856,10 @@
         <v>52</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>56</v>
@@ -1532,40 +1867,71 @@
       <c r="H25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I25" s="4">
+      <c r="I25" s="8">
         <v>1.89380530973451E-4</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I27" s="10"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H30" s="11"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H31" s="12"/>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="11"/>
-    </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H36" s="10"/>
+      <c r="J25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H31" s="10"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H33" s="9"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H36" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{60DA4C04-C08C-42E7-81A2-6ED32579CCCF}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J25">
+  <autoFilter ref="A1:M1" xr:uid="{60DA4C04-C08C-42E7-81A2-6ED32579CCCF}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M25">
       <sortCondition descending="1" ref="F1"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="E2:G5 C2:D25 I3:I4 H3:H5 G6:I6 E6:F15 I7:I8 G7:H15 I10:I15 E16:H25 I19:I20 I24">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="TRUE">
+  <conditionalFormatting sqref="E2:G5 C2:D25 I3:I4 H3:H5 G6:I6 E6:F15 I7:I8 G7:H15 I10 I11:L15 E16:H25 I19:L20 I24">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J17">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",J17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16:L16">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",J16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J21:L21">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",J21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J24:L25">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",J24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{A8CD6070-7DEA-42E0-B1E9-264105A521A4}"/>
-    <hyperlink ref="J7" r:id="rId2" display="https://news.metal.com/newscontent/101559455/the-output-of-lithium-salt-in-qinghai-is-close-to-100000-tons-year-and-the-world-class-industrial-base-of-extracting-lithium-from-salt-lake-is-ready-to-be-developed" xr:uid="{E8A8A58C-2E8D-432F-9EB4-4E8E7497444B}"/>
-    <hyperlink ref="J12" r:id="rId3" xr:uid="{3945ED2C-5F0D-4E4F-BAF7-9FA1395D0488}"/>
+    <hyperlink ref="M5" r:id="rId1" xr:uid="{A8CD6070-7DEA-42E0-B1E9-264105A521A4}"/>
+    <hyperlink ref="M7" r:id="rId2" display="https://news.metal.com/newscontent/101559455/the-output-of-lithium-salt-in-qinghai-is-close-to-100000-tons-year-and-the-world-class-industrial-base-of-extracting-lithium-from-salt-lake-is-ready-to-be-developed" xr:uid="{E8A8A58C-2E8D-432F-9EB4-4E8E7497444B}"/>
+    <hyperlink ref="M12" r:id="rId3" xr:uid="{3945ED2C-5F0D-4E4F-BAF7-9FA1395D0488}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
